--- a/data/trans_camb/IP17-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 9,67</t>
+          <t>-10,47; 10,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 2,03</t>
+          <t>-17,65; 2,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -0,74</t>
+          <t>-24,38; -2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 16,5</t>
+          <t>-2,71; 16,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 10,68</t>
+          <t>-8,86; 11,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 7,35</t>
+          <t>-13,11; 8,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 9,98</t>
+          <t>-3,14; 11,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 3,2</t>
+          <t>-9,5; 3,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -0,26</t>
+          <t>-15,72; 0,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 28,18</t>
+          <t>-21,96; 31,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 6,01</t>
+          <t>-39,24; 8,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,23; -1,43</t>
+          <t>-52,85; -4,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 59,92</t>
+          <t>-6,86; 60,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 38,47</t>
+          <t>-23,86; 42,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 27,01</t>
+          <t>-35,52; 31,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 30,75</t>
+          <t>-8,29; 33,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 9,51</t>
+          <t>-23,4; 10,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 0,04</t>
+          <t>-39,92; 1,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,91</t>
+          <t>-2,17; 9,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,71</t>
+          <t>-5,87; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 3,95</t>
+          <t>-7,97; 5,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,52</t>
+          <t>-5,96; 6,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 1,04</t>
+          <t>-11,58; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 1,45</t>
+          <t>-11,99; 0,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,48</t>
+          <t>-1,98; 6,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 2,02</t>
+          <t>-6,57; 2,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 0,64</t>
+          <t>-8,5; 1,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 58,69</t>
+          <t>-10,46; 55,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 40,66</t>
+          <t>-24,81; 37,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 23,92</t>
+          <t>-35,72; 33,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 35,75</t>
+          <t>-21,93; 29,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 5,19</t>
+          <t>-42,95; 2,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 8,3</t>
+          <t>-45,13; 3,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 37,57</t>
+          <t>-8,14; 35,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 10,94</t>
+          <t>-27,7; 10,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 3,82</t>
+          <t>-35,88; 6,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 8,96</t>
+          <t>-5,26; 9,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 9,24</t>
+          <t>-5,21; 8,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 10,48</t>
+          <t>-5,07; 9,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -0,09</t>
+          <t>-14,27; 0,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 6,88</t>
+          <t>-7,67; 6,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 5,29</t>
+          <t>-8,9; 5,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 2,3</t>
+          <t>-7,59; 2,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,33</t>
+          <t>-4,26; 5,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 5,38</t>
+          <t>-5,15; 5,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 81,35</t>
+          <t>-28,01; 74,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 80,45</t>
+          <t>-26,46; 75,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 91,15</t>
+          <t>-27,5; 81,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,62; 2,35</t>
+          <t>-61,53; 5,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 46,62</t>
+          <t>-32,92; 40,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 34,06</t>
+          <t>-39,41; 35,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 17,02</t>
+          <t>-37,18; 19,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 35,9</t>
+          <t>-21,23; 39,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 37,26</t>
+          <t>-25,19; 35,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,94</t>
+          <t>-3,78; 7,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 8,57</t>
+          <t>-2,1; 8,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,29</t>
+          <t>-6,68; 2,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 4,21</t>
+          <t>-7,52; 4,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 0,84</t>
+          <t>-11,12; 0,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 3,4</t>
+          <t>-7,81; 4,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,56</t>
+          <t>-4,14; 3,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 2,94</t>
+          <t>-4,97; 2,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,86</t>
+          <t>-5,54; 1,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 84,12</t>
+          <t>-29,03; 99,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 109,63</t>
+          <t>-16,55; 108,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 40,22</t>
+          <t>-50,91; 36,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 32,07</t>
+          <t>-41,8; 30,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 6,87</t>
+          <t>-57,56; 8,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 23,8</t>
+          <t>-40,59; 31,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 29,72</t>
+          <t>-26,65; 34,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 26,12</t>
+          <t>-33,18; 26,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 17,44</t>
+          <t>-36,71; 16,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,06</t>
+          <t>-0,03; 6,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,06</t>
+          <t>-2,53; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,61</t>
+          <t>-8,34; -0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,79</t>
+          <t>-3,24; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,63</t>
+          <t>-6,05; 0,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -1,81</t>
+          <t>-9,17; -2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,32</t>
+          <t>-0,91; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,75</t>
+          <t>-3,54; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,21</t>
+          <t>-7,31; -2,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 39,19</t>
+          <t>-0,15; 38,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 22,67</t>
+          <t>-12,08; 22,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,96; -3,16</t>
+          <t>-38,56; -3,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 17,95</t>
+          <t>-13,33; 18,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 3,17</t>
+          <t>-24,95; 3,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -8,86</t>
+          <t>-36,66; -9,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 22,06</t>
+          <t>-3,93; 21,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 8,35</t>
+          <t>-15,55; 7,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -11,36</t>
+          <t>-33,09; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 10,49</t>
+          <t>-9,99; 11,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 2,66</t>
+          <t>-17,67; 2,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,38; -2,25</t>
+          <t>-24,76; -1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 16,2</t>
+          <t>-3,48; 16,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 11,67</t>
+          <t>-9,0; 10,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 8,72</t>
+          <t>-13,37; 7,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 11,06</t>
+          <t>-2,8; 10,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,74</t>
+          <t>-9,22; 4,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 0,71</t>
+          <t>-14,75; 0,41</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 31,45</t>
+          <t>-21,45; 30,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 8,03</t>
+          <t>-38,33; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,85; -4,75</t>
+          <t>-53,83; -3,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 60,07</t>
+          <t>-8,85; 56,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 42,13</t>
+          <t>-22,36; 35,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 31,53</t>
+          <t>-36,61; 27,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 33,8</t>
+          <t>-7,07; 33,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 10,82</t>
+          <t>-22,9; 13,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 1,77</t>
+          <t>-37,15; 1,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 9,49</t>
+          <t>-2,54; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 6,26</t>
+          <t>-5,26; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 5,28</t>
+          <t>-8,65; 4,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 6,17</t>
+          <t>-4,73; 7,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 0,57</t>
+          <t>-10,7; 0,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 0,78</t>
+          <t>-12,04; 1,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,76</t>
+          <t>-2,06; 6,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,17</t>
+          <t>-6,1; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 1,29</t>
+          <t>-8,12; 0,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 55,07</t>
+          <t>-11,8; 58,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 37,08</t>
+          <t>-23,01; 37,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 33,08</t>
+          <t>-38,29; 27,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 29,66</t>
+          <t>-17,5; 34,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 2,93</t>
+          <t>-39,89; 4,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 3,99</t>
+          <t>-44,74; 6,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 35,06</t>
+          <t>-8,77; 34,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 10,97</t>
+          <t>-25,29; 10,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 6,97</t>
+          <t>-34,37; 4,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 9,02</t>
+          <t>-5,2; 8,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,55</t>
+          <t>-5,44; 8,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 9,4</t>
+          <t>-4,34; 10,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 0,39</t>
+          <t>-13,8; 0,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 6,47</t>
+          <t>-7,88; 6,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,12</t>
+          <t>-9,71; 4,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 2,52</t>
+          <t>-7,96; 2,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,72</t>
+          <t>-4,09; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 5,36</t>
+          <t>-5,36; 5,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 74,25</t>
+          <t>-27,33; 77,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 75,75</t>
+          <t>-29,46; 73,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 81,51</t>
+          <t>-23,1; 85,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 5,18</t>
+          <t>-57,98; 3,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 40,94</t>
+          <t>-33,94; 40,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 35,99</t>
+          <t>-40,68; 30,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 19,2</t>
+          <t>-39,36; 17,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 39,38</t>
+          <t>-19,86; 43,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 35,85</t>
+          <t>-26,61; 34,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,67</t>
+          <t>-3,45; 7,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 8,93</t>
+          <t>-2,03; 9,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,8</t>
+          <t>-6,53; 3,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 4,26</t>
+          <t>-7,46; 3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 0,87</t>
+          <t>-10,52; 0,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 4,1</t>
+          <t>-8,04; 3,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,94</t>
+          <t>-4,53; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,98</t>
+          <t>-5,32; 2,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,89</t>
+          <t>-5,58; 1,77</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 99,35</t>
+          <t>-29,1; 102,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 108,54</t>
+          <t>-17,31; 116,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 36,3</t>
+          <t>-49,45; 43,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 30,36</t>
+          <t>-39,97; 27,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 8,89</t>
+          <t>-58,16; 6,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 31,65</t>
+          <t>-41,75; 30,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 34,56</t>
+          <t>-28,86; 36,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 26,44</t>
+          <t>-35,6; 24,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 16,46</t>
+          <t>-36,81; 15,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,95</t>
+          <t>-0,0; 7,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,08</t>
+          <t>-2,5; 4,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,61</t>
+          <t>-8,27; -0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,78</t>
+          <t>-3,49; 3,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,76</t>
+          <t>-6,22; 0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -2,06</t>
+          <t>-8,53; -1,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,15</t>
+          <t>-0,67; 4,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,51</t>
+          <t>-3,37; 1,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -2,41</t>
+          <t>-7,19; -2,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 38,51</t>
+          <t>0,04; 39,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 22,6</t>
+          <t>-11,5; 24,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,56; -3,14</t>
+          <t>-38,79; -5,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 18,15</t>
+          <t>-14,77; 18,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 3,84</t>
+          <t>-26,01; 4,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -9,59</t>
+          <t>-36,05; -8,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 21,08</t>
+          <t>-3,01; 22,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 7,63</t>
+          <t>-15,05; 7,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -12,02</t>
+          <t>-32,64; -11,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,69</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-7,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-12,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,74</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,05</t>
+          <t>-12,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-7,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 11,18</t>
+          <t>-2,95; 16,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 2,54</t>
+          <t>-8,34; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,76; -1,3</t>
+          <t>-13,3; 8,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 16,0</t>
+          <t>-10,49; 9,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 10,44</t>
+          <t>-18,0; 2,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 7,9</t>
+          <t>-23,26; 0,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 10,77</t>
+          <t>-3,41; 9,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 4,68</t>
+          <t>-9,65; 3,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 0,41</t>
+          <t>-15,37; 0,34</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-8,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-0,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-18,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-31,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,22%</t>
+          <t>-29,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,77%</t>
+          <t>-19,6%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 30,81</t>
+          <t>-7,84; 59,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 7,4</t>
+          <t>-21,51; 38,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,83; -3,82</t>
+          <t>-35,51; 29,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 56,75</t>
+          <t>-22,9; 28,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 35,58</t>
+          <t>-37,75; 6,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 27,43</t>
+          <t>-51,73; 0,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 33,38</t>
+          <t>-8,12; 30,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 13,8</t>
+          <t>-23,42; 9,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 1,66</t>
+          <t>-37,81; 1,82</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,05</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>-2,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-3,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 9,8</t>
+          <t>-5,37; 7,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 6,22</t>
+          <t>-10,72; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 4,59</t>
+          <t>-11,51; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,18</t>
+          <t>-2,04; 9,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 0,93</t>
+          <t>-5,02; 6,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 1,3</t>
+          <t>-8,7; 3,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,8</t>
+          <t>-1,68; 7,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,98</t>
+          <t>-6,41; 2,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,93</t>
+          <t>-8,36; 0,48</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-21,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-23,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-10,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,22%</t>
+          <t>-11,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,16%</t>
+          <t>-17,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 58,35</t>
+          <t>-19,29; 35,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 37,68</t>
+          <t>-39,03; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 27,96</t>
+          <t>-43,82; 9,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 34,96</t>
+          <t>-9,58; 58,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 4,9</t>
+          <t>-22,16; 40,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 6,53</t>
+          <t>-39,92; 23,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 34,01</t>
+          <t>-6,96; 37,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 10,51</t>
+          <t>-26,0; 10,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 4,58</t>
+          <t>-35,01; 3,96</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-6,82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 8,9</t>
+          <t>-13,44; -0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 8,8</t>
+          <t>-7,66; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,32</t>
+          <t>-8,64; 5,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,13</t>
+          <t>-5,27; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 6,32</t>
+          <t>-5,44; 9,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 4,61</t>
+          <t>-5,67; 8,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 2,38</t>
+          <t>-7,47; 2,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,04</t>
+          <t>-4,36; 5,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 5,03</t>
+          <t>-4,97; 4,9</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-35,18%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-1,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-8,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>12,34%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-35,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-1,2%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-10,52%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>-0,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 77,56</t>
+          <t>-58,62; 2,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 73,86</t>
+          <t>-32,95; 46,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 85,13</t>
+          <t>-37,5; 37,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 3,66</t>
+          <t>-26,54; 81,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 40,21</t>
+          <t>-27,64; 80,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 30,68</t>
+          <t>-28,82; 76,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 17,27</t>
+          <t>-36,84; 17,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 43,8</t>
+          <t>-21,63; 35,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 34,17</t>
+          <t>-25,22; 34,54</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,87</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,66</t>
+          <t>-7,37; 4,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,17</t>
+          <t>-10,74; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 3,49</t>
+          <t>-7,49; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,46</t>
+          <t>-3,93; 6,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,7</t>
+          <t>-2,39; 8,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 3,86</t>
+          <t>-5,12; 4,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 4,24</t>
+          <t>-3,94; 3,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,9</t>
+          <t>-5,18; 2,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,77</t>
+          <t>-5,14; 2,62</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-11,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-32,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-11,63%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-14,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-11,85%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-32,86%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,54%</t>
+          <t>-5,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,64%</t>
+          <t>-8,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 102,33</t>
+          <t>-38,39; 32,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 116,03</t>
+          <t>-57,03; 6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 43,21</t>
+          <t>-39,77; 25,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,97; 27,1</t>
+          <t>-33,71; 84,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 6,03</t>
+          <t>-18,53; 109,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 30,15</t>
+          <t>-39,6; 58,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 36,38</t>
+          <t>-26,15; 29,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 24,65</t>
+          <t>-34,64; 26,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 15,67</t>
+          <t>-33,42; 23,13</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,03</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,06</t>
+          <t>-3,38; 3,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,47</t>
+          <t>-6,38; 0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,93</t>
+          <t>-8,71; -1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,86</t>
+          <t>-0,3; 7,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,84</t>
+          <t>-2,89; 4,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -1,93</t>
+          <t>-7,68; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,35</t>
+          <t>-0,73; 4,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,41</t>
+          <t>-3,47; 1,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -2,22</t>
+          <t>-7,07; -2,23</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-22,44%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-23,14%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-11,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,88%</t>
+          <t>-22,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-22,8%</t>
+          <t>-22,37%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,04; 39,78</t>
+          <t>-13,77; 17,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 24,5</t>
+          <t>-26,02; 3,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,79; -5,31</t>
+          <t>-35,76; -7,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 18,8</t>
+          <t>-1,36; 39,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 4,05</t>
+          <t>-13,2; 22,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -8,98</t>
+          <t>-35,76; -4,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 22,02</t>
+          <t>-3,07; 22,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 7,14</t>
+          <t>-15,78; 8,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -11,15</t>
+          <t>-32,1; -11,21</t>
         </is>
       </c>
     </row>
